--- a/Stats Sheet/Round Gaps/Cinema.xlsx
+++ b/Stats Sheet/Round Gaps/Cinema.xlsx
@@ -562,13 +562,13 @@
     <x:t>KOKeowner</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>MarcC5M</x:t>
   </x:si>
   <x:si>
     <x:t>Micale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>Pehnk</x:t>
